--- a/docs/data_excel/260617/[legacy] PMO본부 업무수행 현황_260617.xlsx
+++ b/docs/data_excel/260617/[legacy] PMO본부 업무수행 현황_260617.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mycho\Downloads\_Licentia\Coding\pmo-ops-portal\docs\data_excel\260617\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831C2D16-A72D-4426-957F-3598DC8EAA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE1E027-BED3-4AAC-8209-6CF2C6AD4C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13350" yWindow="-16200" windowWidth="27060" windowHeight="15585" xr2:uid="{176080B0-38EF-42A3-A6E8-F29B9A37D012}"/>
+    <workbookView xWindow="990" yWindow="375" windowWidth="27060" windowHeight="15585" xr2:uid="{176080B0-38EF-42A3-A6E8-F29B9A37D012}"/>
   </bookViews>
   <sheets>
     <sheet name="업무수행현황" sheetId="1" r:id="rId1"/>
@@ -2385,7 +2385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2593,9 +2593,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -2650,15 +2647,6 @@
     <xf numFmtId="14" fontId="26" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2737,93 +2725,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2910,6 +2814,108 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3283,16 +3289,16 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="70"/>
+      <c r="O1" s="69"/>
     </row>
     <row r="2" spans="1:24" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="129">
+      <c r="A3" s="113">
         <v>46174</v>
       </c>
-      <c r="B3" s="129"/>
+      <c r="B3" s="113"/>
       <c r="C3" s="47"/>
       <c r="D3" s="48" t="s">
         <v>1</v>
@@ -3303,62 +3309,62 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108" t="s">
+      <c r="D4" s="104"/>
+      <c r="E4" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108" t="s">
+      <c r="F4" s="104"/>
+      <c r="G4" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108" t="s">
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108" t="s">
+      <c r="O4" s="104"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="116" t="s">
+      <c r="R4" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="S4" s="108" t="s">
+      <c r="S4" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="V4" s="116" t="s">
+      <c r="V4" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="W4" s="116" t="s">
+      <c r="W4" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="X4" s="108" t="s">
+      <c r="X4" s="104" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="34.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="108"/>
-      <c r="B5" s="108"/>
+      <c r="A5" s="104"/>
+      <c r="B5" s="104"/>
       <c r="C5" s="15" t="s">
         <v>17</v>
       </c>
@@ -3401,604 +3407,604 @@
       <c r="P5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="108"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="104"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="104"/>
+      <c r="W5" s="104"/>
+      <c r="X5" s="104"/>
     </row>
-    <row r="6" spans="1:24" s="157" customFormat="1" ht="224.25" x14ac:dyDescent="0.3">
-      <c r="A6" s="146">
+    <row r="6" spans="1:24" s="125" customFormat="1" ht="224.25" x14ac:dyDescent="0.3">
+      <c r="A6" s="114">
         <f>ROW()-5</f>
         <v>1</v>
       </c>
-      <c r="B6" s="147" t="s">
+      <c r="B6" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="148" t="s">
+      <c r="C6" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="149" t="s">
+      <c r="D6" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="149" t="s">
+      <c r="E6" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="149" t="s">
+      <c r="F6" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="150" t="s">
+      <c r="G6" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="149" t="s">
+      <c r="H6" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="149" t="s">
+      <c r="I6" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="147" t="s">
+      <c r="J6" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="151" t="s">
+      <c r="K6" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="152">
+      <c r="L6" s="120">
         <v>45498</v>
       </c>
-      <c r="M6" s="152"/>
-      <c r="N6" s="153" t="s">
+      <c r="M6" s="120"/>
+      <c r="N6" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="154" t="s">
+      <c r="O6" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="154" t="s">
+      <c r="P6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="Q6" s="152">
+      <c r="Q6" s="120">
         <v>45454</v>
       </c>
-      <c r="R6" s="149">
+      <c r="R6" s="117">
         <v>20240540846</v>
       </c>
-      <c r="S6" s="152">
+      <c r="S6" s="120">
         <v>45442</v>
       </c>
-      <c r="T6" s="152" t="s">
+      <c r="T6" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="U6" s="152" t="s">
+      <c r="U6" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="V6" s="149" t="s">
+      <c r="V6" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="W6" s="155" t="s">
+      <c r="W6" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="X6" s="156" t="s">
+      <c r="X6" s="124" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="157" customFormat="1" ht="86.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="146">
+    <row r="7" spans="1:24" s="125" customFormat="1" ht="86.25" x14ac:dyDescent="0.3">
+      <c r="A7" s="114">
         <f t="shared" ref="A7:A26" si="0">ROW()-5</f>
         <v>2</v>
       </c>
-      <c r="B7" s="147" t="s">
+      <c r="B7" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="148" t="s">
+      <c r="C7" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="149" t="s">
+      <c r="D7" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="149"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="150" t="s">
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="118" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="149" t="s">
+      <c r="H7" s="117" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="149" t="s">
+      <c r="I7" s="117" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="147" t="s">
+      <c r="J7" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="151" t="s">
+      <c r="K7" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="152">
+      <c r="L7" s="120">
         <v>45587</v>
       </c>
-      <c r="M7" s="152"/>
-      <c r="N7" s="153" t="s">
+      <c r="M7" s="120"/>
+      <c r="N7" s="121" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="154" t="s">
+      <c r="O7" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="154" t="s">
+      <c r="P7" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="Q7" s="152"/>
-      <c r="R7" s="149"/>
-      <c r="S7" s="152" t="s">
+      <c r="Q7" s="120"/>
+      <c r="R7" s="117"/>
+      <c r="S7" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="T7" s="152" t="s">
+      <c r="T7" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="U7" s="152"/>
-      <c r="V7" s="149"/>
-      <c r="W7" s="155" t="s">
+      <c r="U7" s="120"/>
+      <c r="V7" s="117"/>
+      <c r="W7" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="X7" s="158" t="s">
+      <c r="X7" s="126" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="157" customFormat="1" ht="51.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="146">
+    <row r="8" spans="1:24" s="125" customFormat="1" ht="51.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="114">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B8" s="147" t="s">
+      <c r="B8" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="148" t="s">
+      <c r="C8" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="149" t="s">
+      <c r="D8" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="149"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="150" t="s">
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="149" t="s">
+      <c r="H8" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="149" t="s">
+      <c r="I8" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="147" t="s">
+      <c r="J8" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="151" t="s">
+      <c r="K8" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="152">
+      <c r="L8" s="120">
         <v>45691</v>
       </c>
-      <c r="M8" s="152">
+      <c r="M8" s="120">
         <v>45708</v>
       </c>
-      <c r="N8" s="153" t="s">
+      <c r="N8" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="O8" s="154" t="s">
+      <c r="O8" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="P8" s="154" t="s">
+      <c r="P8" s="122" t="s">
         <v>62</v>
       </c>
-      <c r="Q8" s="152">
+      <c r="Q8" s="120">
         <v>45689</v>
       </c>
-      <c r="R8" s="149" t="s">
+      <c r="R8" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="S8" s="152">
+      <c r="S8" s="120">
         <v>45692</v>
       </c>
-      <c r="T8" s="159" t="s">
+      <c r="T8" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="U8" s="159" t="s">
+      <c r="U8" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="V8" s="149" t="s">
+      <c r="V8" s="117" t="s">
         <v>66</v>
       </c>
-      <c r="W8" s="155" t="s">
+      <c r="W8" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="X8" s="158" t="s">
+      <c r="X8" s="126" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="157" customFormat="1" ht="86.25" x14ac:dyDescent="0.3">
-      <c r="A9" s="146">
+    <row r="9" spans="1:24" s="125" customFormat="1" ht="86.25" x14ac:dyDescent="0.3">
+      <c r="A9" s="114">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B9" s="160" t="s">
+      <c r="B9" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="161" t="s">
+      <c r="C9" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="162" t="s">
+      <c r="D9" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="162" t="s">
+      <c r="E9" s="130" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="162" t="s">
+      <c r="F9" s="130" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="163" t="s">
+      <c r="G9" s="131" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="162" t="s">
+      <c r="H9" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="162" t="s">
+      <c r="I9" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="164" t="s">
+      <c r="J9" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="151" t="s">
+      <c r="K9" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="L9" s="165">
+      <c r="L9" s="133">
         <v>45863</v>
       </c>
-      <c r="M9" s="165">
+      <c r="M9" s="133">
         <v>45881</v>
       </c>
-      <c r="N9" s="166" t="s">
+      <c r="N9" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="167" t="s">
+      <c r="O9" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="P9" s="167" t="s">
+      <c r="P9" s="135" t="s">
         <v>75</v>
       </c>
-      <c r="Q9" s="165">
+      <c r="Q9" s="133">
         <v>45860</v>
       </c>
-      <c r="R9" s="168" t="s">
+      <c r="R9" s="136" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="169">
+      <c r="S9" s="137">
         <v>45856</v>
       </c>
-      <c r="T9" s="170">
+      <c r="T9" s="138">
         <v>45877</v>
       </c>
-      <c r="U9" s="170" t="s">
+      <c r="U9" s="138" t="s">
         <v>77</v>
       </c>
-      <c r="V9" s="162" t="s">
+      <c r="V9" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="W9" s="171" t="s">
+      <c r="W9" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="X9" s="172" t="s">
+      <c r="X9" s="140" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="157" customFormat="1" ht="309.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="146">
+    <row r="10" spans="1:24" s="125" customFormat="1" ht="309.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B10" s="160" t="s">
+      <c r="B10" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="161" t="s">
+      <c r="C10" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="162" t="s">
+      <c r="D10" s="130" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="173" t="s">
+      <c r="E10" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="162" t="s">
+      <c r="F10" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="163" t="s">
+      <c r="G10" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="162" t="s">
+      <c r="H10" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="162" t="s">
+      <c r="I10" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="J10" s="164" t="s">
+      <c r="J10" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="151" t="s">
+      <c r="K10" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="L10" s="165">
+      <c r="L10" s="133">
         <v>45926</v>
       </c>
-      <c r="M10" s="165"/>
-      <c r="N10" s="153" t="s">
+      <c r="M10" s="133"/>
+      <c r="N10" s="121" t="s">
         <v>87</v>
       </c>
-      <c r="O10" s="154" t="s">
+      <c r="O10" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="154" t="s">
+      <c r="P10" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="Q10" s="165">
+      <c r="Q10" s="133">
         <v>45917</v>
       </c>
-      <c r="R10" s="168"/>
-      <c r="S10" s="169"/>
-      <c r="T10" s="170"/>
-      <c r="U10" s="170"/>
-      <c r="V10" s="162" t="s">
+      <c r="R10" s="136"/>
+      <c r="S10" s="137"/>
+      <c r="T10" s="138"/>
+      <c r="U10" s="138"/>
+      <c r="V10" s="130" t="s">
         <v>90</v>
       </c>
-      <c r="W10" s="171" t="s">
+      <c r="W10" s="139" t="s">
         <v>86</v>
       </c>
-      <c r="X10" s="174" t="s">
+      <c r="X10" s="142" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="387.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="117">
+    <row r="11" spans="1:24" s="125" customFormat="1" ht="387.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="143">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B11" s="119" t="s">
+      <c r="B11" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="121" t="s">
+      <c r="C11" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="138" t="s">
+      <c r="D11" s="146" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="138" t="s">
+      <c r="E11" s="146" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="138" t="s">
+      <c r="F11" s="146" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="140" t="s">
+      <c r="G11" s="147" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="138" t="s">
+      <c r="H11" s="146" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="138" t="s">
+      <c r="I11" s="146" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="142" t="s">
+      <c r="J11" s="148" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="144" t="s">
+      <c r="K11" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="150">
         <v>45965</v>
       </c>
-      <c r="M11" s="127"/>
-      <c r="N11" s="123" t="s">
+      <c r="M11" s="150"/>
+      <c r="N11" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="O11" s="125" t="s">
+      <c r="O11" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="P11" s="125" t="s">
+      <c r="P11" s="152" t="s">
         <v>99</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="150">
         <v>45898</v>
       </c>
-      <c r="R11" s="130"/>
-      <c r="S11" s="132">
+      <c r="R11" s="153"/>
+      <c r="S11" s="154">
         <v>45965</v>
       </c>
-      <c r="T11" s="134" t="s">
+      <c r="T11" s="155" t="s">
         <v>100</v>
       </c>
-      <c r="U11" s="134" t="s">
+      <c r="U11" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="V11" s="138" t="s">
+      <c r="V11" s="146" t="s">
         <v>102</v>
       </c>
-      <c r="W11" s="136" t="s">
+      <c r="W11" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="X11" s="90" t="s">
+      <c r="X11" s="157" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="366.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="118"/>
-      <c r="B12" s="120"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="139"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="145"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="126"/>
-      <c r="P12" s="126"/>
-      <c r="Q12" s="128"/>
-      <c r="R12" s="131"/>
-      <c r="S12" s="133"/>
-      <c r="T12" s="135"/>
-      <c r="U12" s="135"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="137"/>
-      <c r="X12" s="89" t="s">
+    <row r="12" spans="1:24" s="125" customFormat="1" ht="362.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="158"/>
+      <c r="B12" s="159"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="161"/>
+      <c r="E12" s="161"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="162"/>
+      <c r="H12" s="161"/>
+      <c r="I12" s="161"/>
+      <c r="J12" s="163"/>
+      <c r="K12" s="164"/>
+      <c r="L12" s="165"/>
+      <c r="M12" s="165"/>
+      <c r="N12" s="166"/>
+      <c r="O12" s="167"/>
+      <c r="P12" s="167"/>
+      <c r="Q12" s="165"/>
+      <c r="R12" s="168"/>
+      <c r="S12" s="169"/>
+      <c r="T12" s="170"/>
+      <c r="U12" s="170"/>
+      <c r="V12" s="161"/>
+      <c r="W12" s="171"/>
+      <c r="X12" s="172" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="18" customFormat="1" ht="61.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+    <row r="13" spans="1:24" s="175" customFormat="1" ht="61.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="114">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="56" t="s">
+      <c r="D13" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E13" s="130" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="56" t="s">
+      <c r="F13" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="56" t="s">
+      <c r="H13" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="I13" s="56" t="s">
+      <c r="I13" s="130" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="58" t="s">
+      <c r="J13" s="132" t="s">
         <v>111</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="119" t="s">
         <v>112</v>
       </c>
-      <c r="L13" s="59">
+      <c r="L13" s="133">
         <v>46037</v>
       </c>
-      <c r="M13" s="59">
+      <c r="M13" s="133">
         <v>46094</v>
       </c>
-      <c r="N13" s="60" t="s">
+      <c r="N13" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="O13" s="61" t="s">
+      <c r="O13" s="122" t="s">
         <v>114</v>
       </c>
-      <c r="P13" s="61" t="s">
+      <c r="P13" s="122" t="s">
         <v>115</v>
       </c>
-      <c r="Q13" s="59">
+      <c r="Q13" s="133">
         <v>46017</v>
       </c>
-      <c r="R13" s="62" t="s">
+      <c r="R13" s="136" t="s">
         <v>116</v>
       </c>
-      <c r="S13" s="63">
+      <c r="S13" s="137">
         <v>46049</v>
       </c>
-      <c r="T13" s="69">
+      <c r="T13" s="138">
         <v>46091</v>
       </c>
-      <c r="U13" s="69">
+      <c r="U13" s="138">
         <v>46094</v>
       </c>
-      <c r="V13" s="56" t="s">
+      <c r="V13" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="W13" s="65" t="s">
+      <c r="W13" s="139" t="s">
         <v>118</v>
       </c>
-      <c r="X13" s="88" t="s">
+      <c r="X13" s="174" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="18" customFormat="1" ht="57.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+    <row r="14" spans="1:24" s="175" customFormat="1" ht="57.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="114">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="130" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="130" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="130" t="s">
         <v>124</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="130" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="23" t="s">
+      <c r="J14" s="132" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="119" t="s">
         <v>112</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="133">
         <v>46052</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="133">
         <v>46063</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="O14" s="122" t="s">
         <v>126</v>
       </c>
-      <c r="P14" s="5" t="s">
+      <c r="P14" s="122" t="s">
         <v>127</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="133">
         <v>46035</v>
       </c>
-      <c r="R14" s="26"/>
-      <c r="S14" s="27">
+      <c r="R14" s="136"/>
+      <c r="S14" s="137">
         <v>46051</v>
       </c>
-      <c r="T14" s="28">
+      <c r="T14" s="176">
         <v>46062</v>
       </c>
-      <c r="U14" s="28" t="s">
+      <c r="U14" s="176" t="s">
         <v>128</v>
       </c>
-      <c r="V14" s="21" t="s">
+      <c r="V14" s="130" t="s">
         <v>129</v>
       </c>
-      <c r="W14" s="29" t="s">
+      <c r="W14" s="139" t="s">
         <v>130</v>
       </c>
-      <c r="X14" s="30" t="s">
+      <c r="X14" s="140" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4148,13 +4154,13 @@
       <c r="C17" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="71" t="s">
+      <c r="E17" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="71" t="s">
+      <c r="F17" s="70" t="s">
         <v>149</v>
       </c>
       <c r="G17" s="68" t="s">
@@ -4275,7 +4281,7 @@
       <c r="U18" s="28">
         <v>46133</v>
       </c>
-      <c r="V18" s="80" t="s">
+      <c r="V18" s="79" t="s">
         <v>165</v>
       </c>
       <c r="W18" s="29" t="s">
@@ -4286,17 +4292,17 @@
       </c>
     </row>
     <row r="19" spans="1:24" s="18" customFormat="1" ht="51.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="93">
+      <c r="A19" s="89">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="90" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="97" t="s">
+      <c r="D19" s="93" t="s">
         <v>120</v>
       </c>
       <c r="E19" s="7"/>
@@ -4338,10 +4344,10 @@
       <c r="S19" s="13">
         <v>46094</v>
       </c>
-      <c r="T19" s="95">
+      <c r="T19" s="91">
         <v>46104</v>
       </c>
-      <c r="U19" s="95" t="s">
+      <c r="U19" s="91" t="s">
         <v>171</v>
       </c>
       <c r="V19" s="7" t="s">
@@ -4350,7 +4356,7 @@
       <c r="W19" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="X19" s="96" t="s">
+      <c r="X19" s="92" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4417,7 +4423,7 @@
       <c r="U20" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="V20" s="80" t="s">
+      <c r="V20" s="79" t="s">
         <v>165</v>
       </c>
       <c r="W20" s="29" t="s">
@@ -4428,7 +4434,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" s="18" customFormat="1" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="93">
+      <c r="A21" s="89">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -4438,65 +4444,65 @@
       <c r="C21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="97" t="s">
+      <c r="D21" s="93" t="s">
         <v>181</v>
       </c>
-      <c r="E21" s="97" t="s">
+      <c r="E21" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="F21" s="97" t="s">
+      <c r="F21" s="93" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="98" t="s">
+      <c r="G21" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="H21" s="97" t="s">
+      <c r="H21" s="93" t="s">
         <v>183</v>
       </c>
-      <c r="I21" s="97" t="s">
+      <c r="I21" s="93" t="s">
         <v>184</v>
       </c>
-      <c r="J21" s="99" t="s">
+      <c r="J21" s="95" t="s">
         <v>111</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L21" s="100">
+      <c r="L21" s="96">
         <v>46112</v>
       </c>
-      <c r="M21" s="100">
+      <c r="M21" s="96">
         <v>46121</v>
       </c>
-      <c r="N21" s="101" t="s">
+      <c r="N21" s="97" t="s">
         <v>113</v>
       </c>
-      <c r="O21" s="102" t="s">
+      <c r="O21" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="P21" s="102" t="s">
+      <c r="P21" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="Q21" s="100">
+      <c r="Q21" s="96">
         <v>46111</v>
       </c>
-      <c r="R21" s="103"/>
-      <c r="S21" s="104">
+      <c r="R21" s="99"/>
+      <c r="S21" s="100">
         <v>46107</v>
       </c>
-      <c r="T21" s="104">
+      <c r="T21" s="100">
         <v>46119</v>
       </c>
-      <c r="U21" s="105" t="s">
+      <c r="U21" s="101" t="s">
         <v>186</v>
       </c>
-      <c r="V21" s="97" t="s">
+      <c r="V21" s="93" t="s">
         <v>187</v>
       </c>
-      <c r="W21" s="106" t="s">
+      <c r="W21" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="X21" s="107" t="s">
+      <c r="X21" s="103" t="s">
         <v>188</v>
       </c>
     </row>
@@ -4520,10 +4526,10 @@
       <c r="F22" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="G22" s="82" t="s">
+      <c r="G22" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="H22" s="71" t="s">
+      <c r="H22" s="70" t="s">
         <v>191</v>
       </c>
       <c r="I22" s="56" t="s">
@@ -4556,10 +4562,10 @@
       <c r="R22" s="62" t="s">
         <v>195</v>
       </c>
-      <c r="S22" s="83">
+      <c r="S22" s="82">
         <v>46118</v>
       </c>
-      <c r="T22" s="83">
+      <c r="T22" s="82">
         <v>46129</v>
       </c>
       <c r="U22" s="64">
@@ -4576,7 +4582,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="18" customFormat="1" ht="103.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="84">
+      <c r="A23" s="83">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -4598,13 +4604,13 @@
       <c r="G23" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="H23" s="71" t="s">
+      <c r="H23" s="70" t="s">
         <v>201</v>
       </c>
       <c r="I23" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="J23" s="85" t="s">
+      <c r="J23" s="84" t="s">
         <v>111</v>
       </c>
       <c r="K23" s="24" t="s">
@@ -4619,23 +4625,23 @@
       <c r="N23" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="O23" s="86" t="s">
+      <c r="O23" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="P23" s="86" t="s">
+      <c r="P23" s="85" t="s">
         <v>164</v>
       </c>
       <c r="Q23" s="59">
         <v>46118</v>
       </c>
       <c r="R23" s="62"/>
-      <c r="S23" s="83">
+      <c r="S23" s="82">
         <v>46118</v>
       </c>
-      <c r="T23" s="83">
+      <c r="T23" s="82">
         <v>46125</v>
       </c>
-      <c r="U23" s="87" t="s">
+      <c r="U23" s="86" t="s">
         <v>203</v>
       </c>
       <c r="V23" s="56" t="s">
@@ -4667,7 +4673,7 @@
       <c r="G24" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="H24" s="72" t="s">
+      <c r="H24" s="71" t="s">
         <v>208</v>
       </c>
       <c r="I24" s="21" t="s">
@@ -4741,7 +4747,7 @@
       <c r="L25" s="25">
         <v>46149</v>
       </c>
-      <c r="M25" s="91"/>
+      <c r="M25" s="87"/>
       <c r="N25" s="60" t="s">
         <v>113</v>
       </c>
@@ -4765,11 +4771,11 @@
       </c>
     </row>
     <row r="26" spans="1:24" s="18" customFormat="1" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="93">
+      <c r="A26" s="89">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="90" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -4821,10 +4827,10 @@
       <c r="S26" s="13">
         <v>46153</v>
       </c>
-      <c r="T26" s="95">
+      <c r="T26" s="91">
         <v>46162</v>
       </c>
-      <c r="U26" s="95">
+      <c r="U26" s="91">
         <v>46169</v>
       </c>
       <c r="V26" s="7" t="s">
@@ -4833,7 +4839,7 @@
       <c r="W26" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="X26" s="96" t="s">
+      <c r="X26" s="92" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4847,18 +4853,18 @@
       <c r="C27" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="73" t="s">
+      <c r="D27" s="72" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74" t="s">
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="73" t="s">
         <v>225</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="I27" s="73" t="s">
+      <c r="I27" s="72" t="s">
         <v>227</v>
       </c>
       <c r="J27" s="23" t="s">
@@ -4870,7 +4876,7 @@
       <c r="L27" s="25">
         <v>46154</v>
       </c>
-      <c r="M27" s="75">
+      <c r="M27" s="74">
         <v>46159</v>
       </c>
       <c r="N27" s="4" t="s">
@@ -4882,11 +4888,11 @@
       <c r="P27" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="Q27" s="75">
+      <c r="Q27" s="74">
         <v>46140</v>
       </c>
-      <c r="R27" s="77"/>
-      <c r="S27" s="78">
+      <c r="R27" s="76"/>
+      <c r="S27" s="77">
         <v>46175</v>
       </c>
       <c r="T27" s="28">
@@ -4895,11 +4901,11 @@
       <c r="U27" s="28">
         <v>46202</v>
       </c>
-      <c r="V27" s="73"/>
+      <c r="V27" s="72"/>
       <c r="W27" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="X27" s="79" t="s">
+      <c r="X27" s="78" t="s">
         <v>230</v>
       </c>
     </row>
@@ -4913,22 +4919,22 @@
       <c r="C28" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="73" t="s">
+      <c r="D28" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="E28" s="73" t="s">
+      <c r="E28" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="73" t="s">
+      <c r="F28" s="72" t="s">
         <v>149</v>
       </c>
-      <c r="G28" s="74" t="s">
+      <c r="G28" s="73" t="s">
         <v>231</v>
       </c>
       <c r="H28" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="I28" s="73" t="s">
+      <c r="I28" s="72" t="s">
         <v>143</v>
       </c>
       <c r="J28" s="23" t="s">
@@ -4937,25 +4943,25 @@
       <c r="K28" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="L28" s="75">
+      <c r="L28" s="74">
         <v>46160</v>
       </c>
-      <c r="M28" s="75">
+      <c r="M28" s="74">
         <v>46177</v>
       </c>
       <c r="N28" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="O28" s="76" t="s">
+      <c r="O28" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="P28" s="76" t="s">
+      <c r="P28" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="Q28" s="75">
+      <c r="Q28" s="74">
         <v>46156</v>
       </c>
-      <c r="R28" s="77"/>
+      <c r="R28" s="76"/>
       <c r="S28" s="27">
         <v>46161</v>
       </c>
@@ -4965,13 +4971,13 @@
       <c r="U28" s="28">
         <v>46177</v>
       </c>
-      <c r="V28" s="73" t="s">
+      <c r="V28" s="72" t="s">
         <v>204</v>
       </c>
       <c r="W28" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="X28" s="79" t="s">
+      <c r="X28" s="78" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4988,46 +4994,46 @@
       <c r="D29" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
       <c r="G29" s="22" t="s">
         <v>234</v>
       </c>
       <c r="H29" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="I29" s="73" t="s">
+      <c r="I29" s="72" t="s">
         <v>236</v>
       </c>
       <c r="J29" s="23"/>
       <c r="K29" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="L29" s="75">
+      <c r="L29" s="74">
         <v>46169</v>
       </c>
-      <c r="M29" s="92"/>
+      <c r="M29" s="88"/>
       <c r="N29" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O29" s="76" t="s">
+      <c r="O29" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="P29" s="76" t="s">
+      <c r="P29" s="75" t="s">
         <v>238</v>
       </c>
-      <c r="Q29" s="75">
+      <c r="Q29" s="74">
         <v>46169</v>
       </c>
-      <c r="R29" s="77"/>
-      <c r="S29" s="78"/>
+      <c r="R29" s="76"/>
+      <c r="S29" s="77"/>
       <c r="T29" s="28"/>
       <c r="U29" s="28"/>
-      <c r="V29" s="73"/>
+      <c r="V29" s="72"/>
       <c r="W29" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="X29" s="79" t="s">
+      <c r="X29" s="78" t="s">
         <v>239</v>
       </c>
     </row>
@@ -5038,25 +5044,25 @@
       <c r="B30" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="73" t="s">
+      <c r="C30" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="73" t="s">
+      <c r="D30" s="72" t="s">
         <v>240</v>
       </c>
-      <c r="E30" s="73" t="s">
+      <c r="E30" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="73" t="s">
+      <c r="F30" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G30" s="74" t="s">
+      <c r="G30" s="73" t="s">
         <v>241</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="I30" s="73" t="s">
+      <c r="I30" s="72" t="s">
         <v>243</v>
       </c>
       <c r="J30" s="23" t="s">
@@ -5065,28 +5071,28 @@
       <c r="K30" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="L30" s="75">
+      <c r="L30" s="74">
         <v>46170</v>
       </c>
-      <c r="M30" s="75">
+      <c r="M30" s="74">
         <v>46182</v>
       </c>
       <c r="N30" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="O30" s="76" t="s">
+      <c r="O30" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="P30" s="76" t="s">
+      <c r="P30" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="Q30" s="75">
+      <c r="Q30" s="74">
         <v>46170</v>
       </c>
-      <c r="R30" s="77" t="s">
+      <c r="R30" s="76" t="s">
         <v>244</v>
       </c>
-      <c r="S30" s="78">
+      <c r="S30" s="77">
         <v>46146</v>
       </c>
       <c r="T30" s="28">
@@ -5099,7 +5105,7 @@
       <c r="W30" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="X30" s="79" t="s">
+      <c r="X30" s="78" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5113,18 +5119,18 @@
       <c r="C31" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="73" t="s">
+      <c r="D31" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="74" t="s">
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="73" t="s">
         <v>247</v>
       </c>
-      <c r="H31" s="73" t="s">
+      <c r="H31" s="72" t="s">
         <v>248</v>
       </c>
-      <c r="I31" s="73" t="s">
+      <c r="I31" s="72" t="s">
         <v>249</v>
       </c>
       <c r="J31" s="23" t="s">
@@ -5133,35 +5139,35 @@
       <c r="K31" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="L31" s="75">
+      <c r="L31" s="74">
         <v>46184</v>
       </c>
-      <c r="M31" s="75">
+      <c r="M31" s="74">
         <v>46184</v>
       </c>
       <c r="N31" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="O31" s="76" t="s">
+      <c r="O31" s="75" t="s">
         <v>126</v>
       </c>
-      <c r="P31" s="76" t="s">
+      <c r="P31" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="Q31" s="75">
+      <c r="Q31" s="74">
         <v>46184</v>
       </c>
-      <c r="R31" s="77"/>
-      <c r="S31" s="78"/>
+      <c r="R31" s="76"/>
+      <c r="S31" s="77"/>
       <c r="T31" s="28">
         <v>46190</v>
       </c>
       <c r="U31" s="28"/>
-      <c r="V31" s="73"/>
+      <c r="V31" s="72"/>
       <c r="W31" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="X31" s="79" t="s">
+      <c r="X31" s="78" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5175,18 +5181,18 @@
       <c r="C32" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="73" t="s">
+      <c r="D32" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="74" t="s">
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="73" t="s">
         <v>251</v>
       </c>
-      <c r="H32" s="73" t="s">
+      <c r="H32" s="72" t="s">
         <v>252</v>
       </c>
-      <c r="I32" s="73" t="s">
+      <c r="I32" s="72" t="s">
         <v>253</v>
       </c>
       <c r="J32" s="23" t="s">
@@ -5195,35 +5201,35 @@
       <c r="K32" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="L32" s="75">
+      <c r="L32" s="74">
         <v>46185</v>
       </c>
-      <c r="M32" s="75">
+      <c r="M32" s="74">
         <v>46185</v>
       </c>
       <c r="N32" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="O32" s="76" t="s">
+      <c r="O32" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="P32" s="76" t="s">
+      <c r="P32" s="75" t="s">
         <v>254</v>
       </c>
-      <c r="Q32" s="75">
+      <c r="Q32" s="74">
         <v>46184</v>
       </c>
-      <c r="R32" s="77"/>
-      <c r="S32" s="78"/>
+      <c r="R32" s="76"/>
+      <c r="S32" s="77"/>
       <c r="T32" s="28">
         <v>46190</v>
       </c>
       <c r="U32" s="28"/>
-      <c r="V32" s="73"/>
+      <c r="V32" s="72"/>
       <c r="W32" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="X32" s="79" t="s">
+      <c r="X32" s="78" t="s">
         <v>255</v>
       </c>
     </row>
@@ -5237,22 +5243,22 @@
       <c r="C33" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="73" t="s">
+      <c r="D33" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="73" t="s">
+      <c r="E33" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="73" t="s">
+      <c r="F33" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="74" t="s">
+      <c r="G33" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="H33" s="73" t="s">
+      <c r="H33" s="72" t="s">
         <v>257</v>
       </c>
-      <c r="I33" s="73" t="s">
+      <c r="I33" s="72" t="s">
         <v>258</v>
       </c>
       <c r="J33" s="23" t="s">
@@ -5261,31 +5267,31 @@
       <c r="K33" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="L33" s="75">
+      <c r="L33" s="74">
         <v>46195</v>
       </c>
-      <c r="M33" s="75"/>
+      <c r="M33" s="74"/>
       <c r="N33" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="O33" s="76" t="s">
+      <c r="O33" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="P33" s="76" t="s">
+      <c r="P33" s="75" t="s">
         <v>259</v>
       </c>
-      <c r="Q33" s="75">
+      <c r="Q33" s="74">
         <v>46195</v>
       </c>
-      <c r="R33" s="77"/>
-      <c r="S33" s="78"/>
+      <c r="R33" s="76"/>
+      <c r="S33" s="77"/>
       <c r="T33" s="28"/>
       <c r="U33" s="28"/>
-      <c r="V33" s="73"/>
+      <c r="V33" s="72"/>
       <c r="W33" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="X33" s="79" t="s">
+      <c r="X33" s="78" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5295,27 +5301,27 @@
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
       <c r="J34" s="23"/>
       <c r="K34" s="24"/>
-      <c r="L34" s="75"/>
-      <c r="M34" s="75"/>
+      <c r="L34" s="74"/>
+      <c r="M34" s="74"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="76"/>
-      <c r="Q34" s="75"/>
-      <c r="R34" s="77"/>
-      <c r="S34" s="78"/>
+      <c r="O34" s="75"/>
+      <c r="P34" s="75"/>
+      <c r="Q34" s="74"/>
+      <c r="R34" s="76"/>
+      <c r="S34" s="77"/>
       <c r="T34" s="28"/>
       <c r="U34" s="28"/>
-      <c r="V34" s="73"/>
+      <c r="V34" s="72"/>
       <c r="W34" s="29"/>
-      <c r="X34" s="79"/>
+      <c r="X34" s="78"/>
     </row>
     <row r="35" spans="1:24" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17">
@@ -5323,27 +5329,27 @@
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="20"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="72"/>
       <c r="J35" s="23"/>
       <c r="K35" s="24"/>
-      <c r="L35" s="75"/>
-      <c r="M35" s="75"/>
+      <c r="L35" s="74"/>
+      <c r="M35" s="74"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="75"/>
-      <c r="R35" s="77"/>
-      <c r="S35" s="78"/>
+      <c r="O35" s="75"/>
+      <c r="P35" s="75"/>
+      <c r="Q35" s="74"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="77"/>
       <c r="T35" s="28"/>
       <c r="U35" s="28"/>
-      <c r="V35" s="73"/>
+      <c r="V35" s="72"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="79"/>
+      <c r="X35" s="78"/>
     </row>
     <row r="36" spans="1:24" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="17">
@@ -5351,27 +5357,27 @@
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="20"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
       <c r="J36" s="23"/>
       <c r="K36" s="24"/>
-      <c r="L36" s="75"/>
-      <c r="M36" s="75"/>
+      <c r="L36" s="74"/>
+      <c r="M36" s="74"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="76"/>
-      <c r="Q36" s="75"/>
-      <c r="R36" s="77"/>
-      <c r="S36" s="78"/>
+      <c r="O36" s="75"/>
+      <c r="P36" s="75"/>
+      <c r="Q36" s="74"/>
+      <c r="R36" s="76"/>
+      <c r="S36" s="77"/>
       <c r="T36" s="28"/>
       <c r="U36" s="28"/>
-      <c r="V36" s="73"/>
+      <c r="V36" s="72"/>
       <c r="W36" s="29"/>
-      <c r="X36" s="79"/>
+      <c r="X36" s="78"/>
     </row>
     <row r="37" spans="1:24" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17">
@@ -5379,46 +5385,46 @@
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="20"/>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="72"/>
+      <c r="I37" s="72"/>
       <c r="J37" s="23"/>
       <c r="K37" s="24"/>
-      <c r="L37" s="75"/>
-      <c r="M37" s="75"/>
+      <c r="L37" s="74"/>
+      <c r="M37" s="74"/>
       <c r="N37" s="4"/>
-      <c r="O37" s="76"/>
-      <c r="P37" s="76"/>
-      <c r="Q37" s="75"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="78"/>
+      <c r="O37" s="75"/>
+      <c r="P37" s="75"/>
+      <c r="Q37" s="74"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="77"/>
       <c r="T37" s="28"/>
       <c r="U37" s="28"/>
-      <c r="V37" s="73"/>
+      <c r="V37" s="72"/>
       <c r="W37" s="29"/>
-      <c r="X37" s="79"/>
+      <c r="X37" s="78"/>
     </row>
     <row r="38" spans="1:24" s="39" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A38" s="109" t="s">
+      <c r="A38" s="105" t="s">
         <v>261</v>
       </c>
-      <c r="B38" s="110"/>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="110"/>
+      <c r="B38" s="106"/>
+      <c r="C38" s="106"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="106"/>
       <c r="H38" s="31"/>
       <c r="I38" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="J38" s="111">
+      <c r="J38" s="107">
         <v>17</v>
       </c>
-      <c r="K38" s="112"/>
+      <c r="K38" s="108"/>
       <c r="L38" s="33" t="s">
         <v>263</v>
       </c>
@@ -5435,12 +5441,12 @@
       <c r="Q38" s="37">
         <v>4</v>
       </c>
-      <c r="R38" s="113"/>
-      <c r="S38" s="114"/>
-      <c r="T38" s="114"/>
-      <c r="U38" s="114"/>
-      <c r="V38" s="114"/>
-      <c r="W38" s="115"/>
+      <c r="R38" s="109"/>
+      <c r="S38" s="110"/>
+      <c r="T38" s="110"/>
+      <c r="U38" s="110"/>
+      <c r="V38" s="110"/>
+      <c r="W38" s="111"/>
       <c r="X38" s="38" t="s">
         <v>266</v>
       </c>
@@ -5940,14 +5946,14 @@
       <c r="H14" s="42" t="s">
         <v>319</v>
       </c>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="51">
         <v>14</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="80" t="s">
         <v>320</v>
       </c>
       <c r="C15" s="42" t="s">
@@ -5968,14 +5974,14 @@
       <c r="H15" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="51">
         <v>15</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="80" t="s">
         <v>323</v>
       </c>
       <c r="C16" s="42" t="s">
@@ -5996,14 +6002,14 @@
       <c r="H16" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="80"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="51">
         <v>16</v>
       </c>
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="80" t="s">
         <v>325</v>
       </c>
       <c r="C17" s="42" t="s">
@@ -6024,14 +6030,14 @@
       <c r="H17" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>17</v>
       </c>
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="80" t="s">
         <v>327</v>
       </c>
       <c r="C18" s="42" t="s">
@@ -6052,14 +6058,14 @@
       <c r="H18" s="42" t="s">
         <v>319</v>
       </c>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>18</v>
       </c>
-      <c r="B19" s="81" t="s">
+      <c r="B19" s="80" t="s">
         <v>330</v>
       </c>
       <c r="C19" s="42" t="s">
@@ -6080,14 +6086,14 @@
       <c r="H19" s="51" t="s">
         <v>332</v>
       </c>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="51">
         <v>19</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="80" t="s">
         <v>333</v>
       </c>
       <c r="C20" s="42" t="s">
@@ -6108,14 +6114,14 @@
       <c r="H20" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>20</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="80" t="s">
         <v>335</v>
       </c>
       <c r="C21" s="42" t="s">
@@ -6136,14 +6142,14 @@
       <c r="H21" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="51">
         <v>21</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="80" t="s">
         <v>337</v>
       </c>
       <c r="C22" s="42" t="s">
@@ -6164,64 +6170,64 @@
       <c r="H22" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="51">
         <v>22</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="51"/>
       <c r="G23" s="51"/>
       <c r="H23" s="51"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="51">
         <v>23</v>
       </c>
-      <c r="B24" s="81"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
       <c r="F24" s="51"/>
       <c r="G24" s="51"/>
       <c r="H24" s="51"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="51">
         <v>24</v>
       </c>
-      <c r="B25" s="81"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="81"/>
-      <c r="E25" s="81"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
       <c r="F25" s="51"/>
       <c r="G25" s="51"/>
       <c r="H25" s="51"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="81"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="51">
         <v>25</v>
       </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="51"/>
       <c r="G26" s="51"/>
       <c r="H26" s="51"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
